--- a/app1/Excelfiles/April2024_150000.xlsx
+++ b/app1/Excelfiles/April2024_150000.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,13 +443,20 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
     <row r="5"/>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
